--- a/sheets/대금율보/검수/남창 질음시조.xlsx
+++ b/sheets/대금율보/검수/남창 질음시조.xlsx
@@ -4134,8 +4134,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌇
-‹</t>
+          <t xml:space="preserve">⌇</t>
         </is>
       </c>
       <c r="E4" s="22"/>
@@ -4198,8 +4197,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林ㄴ⌇
-‹</t>
+          <t xml:space="preserve">林ㄴ⌇</t>
         </is>
       </c>
       <c r="C5" s="22"/>
@@ -4267,8 +4265,7 @@
         <is>
           <t xml:space="preserve">h仲⌇
 –林ʒ
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="S5" s="22"/>
@@ -4368,8 +4365,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –И
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -4377,8 +4373,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-黃И
-‹</t>
+黃И</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -4392,8 +4387,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="K7" s="22"/>
@@ -4401,8 +4395,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-黃И
-‹</t>
+黃И</t>
         </is>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -4414,8 +4407,7 @@
       <c r="O7" s="22"/>
       <c r="P7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林⌇
-‹</t>
+          <t xml:space="preserve">林⌇</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
@@ -4586,8 +4578,7 @@
         <is>
           <t xml:space="preserve">林ㄴ⌇
 –И
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="E10" s="22"/>
@@ -4603,8 +4594,7 @@
         <is>
           <t xml:space="preserve">仲ㄴ
 太∧黃⌇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -4616,8 +4606,7 @@
         <is>
           <t xml:space="preserve">仲
 –⌇
-И
-‹</t>
+И</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
@@ -4649,8 +4638,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-汰)
-‹</t>
+汰)</t>
         </is>
       </c>
       <c r="Q10" s="22"/>
@@ -4752,8 +4740,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-太)
-‹</t>
+太)</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4761,8 +4748,7 @@
         <is>
           <t xml:space="preserve">–μ
 林⌇
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -4774,8 +4760,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –汰∧
-汰フ
-‹</t>
+汰フ</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -4783,8 +4768,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-太
-‹</t>
+太</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -4792,8 +4776,7 @@
         <is>
           <t xml:space="preserve">南フ⌇
 –И
-Z
-‹</t>
+Z</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -4801,8 +4784,7 @@
         <is>
           <t xml:space="preserve">汰ㄴ
 –
-–Z
-‹</t>
+–Z</t>
         </is>
       </c>
       <c r="Q12" s="22"/>
@@ -5013,8 +4995,7 @@
         <is>
           <t xml:space="preserve">潢ʒh
 仲
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="O15" s="22" t="inlineStr">

--- a/sheets/대금율보/검수/남창 질음시조.xlsx
+++ b/sheets/대금율보/검수/남창 질음시조.xlsx
@@ -3983,30 +3983,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="16.2" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.2" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="16.2" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="16.2" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="95.24" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="131.1" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="131.1" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="131.1" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="131.1" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="131.1" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="131.1" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="131.1" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4570,7 +4570,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="131.1" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -4645,7 +4645,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="131.1" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4724,7 +4724,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="131.1" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4791,7 +4791,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="131.1" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -4876,7 +4876,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="131.1" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -4941,7 +4941,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="131.1" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5020,6 +5020,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="42"/>
 </worksheet>
 </file>